--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ ЗПФ/дв 02,07,26 бррсч пок зпф.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ ЗПФ/дв 02,07,26 бррсч пок зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B16D4D5-2997-4F4D-AF8E-745012C4FB13}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DD72C6-A21B-4415-A447-5D06759946DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$69</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1015,7 +1015,9 @@
     <col min="32" max="32" width="6" customWidth="1"/>
     <col min="33" max="34" width="5" customWidth="1"/>
     <col min="35" max="35" width="6" style="11" customWidth="1"/>
-    <col min="36" max="44" width="3" customWidth="1"/>
+    <col min="36" max="36" width="7.5703125" customWidth="1"/>
+    <col min="37" max="37" width="7.85546875" customWidth="1"/>
+    <col min="38" max="44" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.25">
@@ -1393,8 +1395,14 @@
         <f>SUM(AI6:AI500)</f>
         <v>15.861111111111112</v>
       </c>
-      <c r="AJ5" s="16"/>
-      <c r="AK5" s="16"/>
+      <c r="AJ5" s="3">
+        <f>SUM(AJ6:AJ500)</f>
+        <v>1037.164</v>
+      </c>
+      <c r="AK5" s="3">
+        <f>SUM(AK6:AK500)</f>
+        <v>6785.2400000000007</v>
+      </c>
       <c r="AL5" s="16"/>
       <c r="AM5" s="16"/>
       <c r="AN5" s="16"/>
@@ -1483,8 +1491,14 @@
       <c r="AG6" s="12"/>
       <c r="AH6" s="12"/>
       <c r="AI6" s="15"/>
-      <c r="AJ6" s="16"/>
-      <c r="AK6" s="16"/>
+      <c r="AJ6" s="16">
+        <f>Q6*G6</f>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="16">
+        <f>P6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AL6" s="16"/>
       <c r="AM6" s="16"/>
       <c r="AN6" s="16"/>
@@ -1575,8 +1589,14 @@
       <c r="AG7" s="12"/>
       <c r="AH7" s="12"/>
       <c r="AI7" s="15"/>
-      <c r="AJ7" s="16"/>
-      <c r="AK7" s="16"/>
+      <c r="AJ7" s="16">
+        <f t="shared" ref="AJ7:AJ69" si="6">Q7*G7</f>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="16">
+        <f t="shared" ref="AK7:AK70" si="7">P7*G7</f>
+        <v>0</v>
+      </c>
       <c r="AL7" s="16"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
@@ -1661,8 +1681,14 @@
       <c r="AG8" s="12"/>
       <c r="AH8" s="12"/>
       <c r="AI8" s="15"/>
-      <c r="AJ8" s="16"/>
-      <c r="AK8" s="16"/>
+      <c r="AJ8" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL8" s="16"/>
       <c r="AM8" s="16"/>
       <c r="AN8" s="16"/>
@@ -1751,8 +1777,14 @@
       <c r="AG9" s="12"/>
       <c r="AH9" s="12"/>
       <c r="AI9" s="15"/>
-      <c r="AJ9" s="16"/>
-      <c r="AK9" s="16"/>
+      <c r="AJ9" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL9" s="16"/>
       <c r="AM9" s="16"/>
       <c r="AN9" s="16"/>
@@ -1809,7 +1841,7 @@
       </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4">
-        <f t="shared" ref="S10:S31" si="6">AD10*AE10</f>
+        <f t="shared" ref="S10:S31" si="8">AD10*AE10</f>
         <v>0</v>
       </c>
       <c r="T10" s="16">
@@ -1840,18 +1872,18 @@
       </c>
       <c r="AB10" s="16"/>
       <c r="AC10" s="16">
-        <f t="shared" ref="AC10:AC19" si="7">G10*R10</f>
+        <f t="shared" ref="AC10:AC19" si="9">G10*R10</f>
         <v>0</v>
       </c>
       <c r="AD10" s="6">
         <v>12</v>
       </c>
       <c r="AE10" s="8">
-        <f t="shared" ref="AE10:AE19" si="8">MROUND(R10, AD10*AG10)/AD10</f>
+        <f t="shared" ref="AE10:AE19" si="10">MROUND(R10, AD10*AG10)/AD10</f>
         <v>0</v>
       </c>
       <c r="AF10" s="16">
-        <f t="shared" ref="AF10:AF19" si="9">AE10*AD10*G10</f>
+        <f t="shared" ref="AF10:AF19" si="11">AE10*AD10*G10</f>
         <v>0</v>
       </c>
       <c r="AG10" s="19">
@@ -1861,11 +1893,17 @@
         <v>70</v>
       </c>
       <c r="AI10" s="8">
-        <f t="shared" ref="AI10:AI31" si="10">AE10/AH10</f>
+        <f t="shared" ref="AI10:AI31" si="12">AE10/AH10</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="16"/>
-      <c r="AK10" s="16"/>
+      <c r="AJ10" s="16">
+        <f t="shared" si="6"/>
+        <v>1.1440000000000001</v>
+      </c>
+      <c r="AK10" s="16">
+        <f t="shared" si="7"/>
+        <v>36.96</v>
+      </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16"/>
       <c r="AN10" s="16"/>
@@ -1925,7 +1963,7 @@
         <v>330.59999999999991</v>
       </c>
       <c r="S11" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>336</v>
       </c>
       <c r="T11" s="16">
@@ -1956,18 +1994,18 @@
       </c>
       <c r="AB11" s="16"/>
       <c r="AC11" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>99.179999999999964</v>
       </c>
       <c r="AD11" s="6">
         <v>12</v>
       </c>
       <c r="AE11" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="AF11" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>100.8</v>
       </c>
       <c r="AG11" s="19">
@@ -1977,11 +2015,17 @@
         <v>70</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
-      <c r="AJ11" s="16"/>
-      <c r="AK11" s="16"/>
+      <c r="AJ11" s="16">
+        <f t="shared" si="6"/>
+        <v>13.139999999999999</v>
+      </c>
+      <c r="AK11" s="16">
+        <f t="shared" si="7"/>
+        <v>50.4</v>
+      </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16"/>
       <c r="AN11" s="16"/>
@@ -2038,7 +2082,7 @@
       </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T12" s="16">
@@ -2069,18 +2113,18 @@
       </c>
       <c r="AB12" s="16"/>
       <c r="AC12" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD12" s="6">
         <v>6</v>
       </c>
       <c r="AE12" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AF12" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AG12" s="19">
@@ -2090,11 +2134,17 @@
         <v>140</v>
       </c>
       <c r="AI12" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ12" s="16"/>
-      <c r="AK12" s="16"/>
+      <c r="AJ12" s="16">
+        <f t="shared" si="6"/>
+        <v>8.9040000000000017</v>
+      </c>
+      <c r="AK12" s="16">
+        <f t="shared" si="7"/>
+        <v>141.12</v>
+      </c>
       <c r="AL12" s="16"/>
       <c r="AM12" s="16"/>
       <c r="AN12" s="16"/>
@@ -2150,11 +2200,11 @@
         <v>100.2</v>
       </c>
       <c r="R13" s="4">
-        <f t="shared" ref="R13:R16" si="11">$R$1*Q13-P13-O13-F13</f>
+        <f t="shared" ref="R13:R16" si="13">$R$1*Q13-P13-O13-F13</f>
         <v>848.40000000000009</v>
       </c>
       <c r="S13" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>840</v>
       </c>
       <c r="T13" s="16">
@@ -2185,18 +2235,18 @@
       </c>
       <c r="AB13" s="16"/>
       <c r="AC13" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>203.61600000000001</v>
       </c>
       <c r="AD13" s="6">
         <v>12</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>70</v>
       </c>
       <c r="AF13" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>201.6</v>
       </c>
       <c r="AG13" s="19">
@@ -2206,11 +2256,17 @@
         <v>70</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AJ13" s="16"/>
-      <c r="AK13" s="16"/>
+      <c r="AJ13" s="16">
+        <f t="shared" si="6"/>
+        <v>24.047999999999998</v>
+      </c>
+      <c r="AK13" s="16">
+        <f t="shared" si="7"/>
+        <v>40.32</v>
+      </c>
       <c r="AL13" s="16"/>
       <c r="AM13" s="16"/>
       <c r="AN13" s="16"/>
@@ -2268,11 +2324,11 @@
         <v>82.8</v>
       </c>
       <c r="R14" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>925.59999999999991</v>
       </c>
       <c r="S14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1008</v>
       </c>
       <c r="T14" s="16">
@@ -2303,18 +2359,18 @@
       </c>
       <c r="AB14" s="16"/>
       <c r="AC14" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>222.14399999999998</v>
       </c>
       <c r="AD14" s="6">
         <v>12</v>
       </c>
       <c r="AE14" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>84</v>
       </c>
       <c r="AF14" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>241.92</v>
       </c>
       <c r="AG14" s="19">
@@ -2324,11 +2380,17 @@
         <v>70</v>
       </c>
       <c r="AI14" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1.2</v>
       </c>
-      <c r="AJ14" s="16"/>
-      <c r="AK14" s="16"/>
+      <c r="AJ14" s="16">
+        <f t="shared" si="6"/>
+        <v>19.872</v>
+      </c>
+      <c r="AK14" s="16">
+        <f t="shared" si="7"/>
+        <v>80.64</v>
+      </c>
       <c r="AL14" s="16"/>
       <c r="AM14" s="16"/>
       <c r="AN14" s="16"/>
@@ -2386,11 +2448,11 @@
         <v>48.6</v>
       </c>
       <c r="R15" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>152.20000000000005</v>
       </c>
       <c r="S15" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>168</v>
       </c>
       <c r="T15" s="16">
@@ -2421,18 +2483,18 @@
       </c>
       <c r="AB15" s="16"/>
       <c r="AC15" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>36.528000000000013</v>
       </c>
       <c r="AD15" s="6">
         <v>12</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AF15" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>40.32</v>
       </c>
       <c r="AG15" s="19">
@@ -2442,11 +2504,17 @@
         <v>70</v>
       </c>
       <c r="AI15" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="AJ15" s="16"/>
-      <c r="AK15" s="16"/>
+      <c r="AJ15" s="16">
+        <f t="shared" si="6"/>
+        <v>11.664</v>
+      </c>
+      <c r="AK15" s="16">
+        <f t="shared" si="7"/>
+        <v>80.64</v>
+      </c>
       <c r="AL15" s="16"/>
       <c r="AM15" s="16"/>
       <c r="AN15" s="16"/>
@@ -2506,11 +2574,11 @@
         <v>89.2</v>
       </c>
       <c r="R16" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>825.40000000000009</v>
       </c>
       <c r="S16" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>840</v>
       </c>
       <c r="T16" s="16">
@@ -2541,18 +2609,18 @@
       </c>
       <c r="AB16" s="16"/>
       <c r="AC16" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>198.096</v>
       </c>
       <c r="AD16" s="6">
         <v>12</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>70</v>
       </c>
       <c r="AF16" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>201.6</v>
       </c>
       <c r="AG16" s="19">
@@ -2562,11 +2630,17 @@
         <v>70</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AJ16" s="16"/>
-      <c r="AK16" s="16"/>
+      <c r="AJ16" s="16">
+        <f t="shared" si="6"/>
+        <v>21.408000000000001</v>
+      </c>
+      <c r="AK16" s="16">
+        <f t="shared" si="7"/>
+        <v>80.64</v>
+      </c>
       <c r="AL16" s="16"/>
       <c r="AM16" s="16"/>
       <c r="AN16" s="16"/>
@@ -2619,7 +2693,7 @@
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T17" s="16">
@@ -2650,18 +2724,18 @@
       </c>
       <c r="AB17" s="16"/>
       <c r="AC17" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD17" s="6">
         <v>8</v>
       </c>
       <c r="AE17" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AF17" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AG17" s="19">
@@ -2671,11 +2745,17 @@
         <v>70</v>
       </c>
       <c r="AI17" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ17" s="16"/>
-      <c r="AK17" s="16"/>
+      <c r="AJ17" s="16">
+        <f t="shared" si="6"/>
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="AK17" s="16">
+        <f t="shared" si="7"/>
+        <v>53.76</v>
+      </c>
       <c r="AL17" s="16"/>
       <c r="AM17" s="16"/>
       <c r="AN17" s="16"/>
@@ -2730,7 +2810,7 @@
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T18" s="16" t="e">
@@ -2761,18 +2841,18 @@
       </c>
       <c r="AB18" s="16"/>
       <c r="AC18" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD18" s="6">
         <v>24</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AF18" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AG18" s="19">
@@ -2782,11 +2862,17 @@
         <v>126</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ18" s="16"/>
-      <c r="AK18" s="16"/>
+      <c r="AJ18" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="16">
+        <f t="shared" si="7"/>
+        <v>30.24</v>
+      </c>
       <c r="AL18" s="16"/>
       <c r="AM18" s="16"/>
       <c r="AN18" s="16"/>
@@ -2846,7 +2932,7 @@
         <v>519</v>
       </c>
       <c r="S19" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>560</v>
       </c>
       <c r="T19" s="16">
@@ -2877,18 +2963,18 @@
       </c>
       <c r="AB19" s="16"/>
       <c r="AC19" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>186.84</v>
       </c>
       <c r="AD19" s="6">
         <v>10</v>
       </c>
       <c r="AE19" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>56</v>
       </c>
       <c r="AF19" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>201.6</v>
       </c>
       <c r="AG19" s="19">
@@ -2898,11 +2984,17 @@
         <v>70</v>
       </c>
       <c r="AI19" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.8</v>
       </c>
-      <c r="AJ19" s="16"/>
-      <c r="AK19" s="16"/>
+      <c r="AJ19" s="16">
+        <f t="shared" si="6"/>
+        <v>16.2</v>
+      </c>
+      <c r="AK19" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL19" s="16"/>
       <c r="AM19" s="16"/>
       <c r="AN19" s="16"/>
@@ -2991,8 +3083,14 @@
       <c r="AG20" s="12"/>
       <c r="AH20" s="12"/>
       <c r="AI20" s="15"/>
-      <c r="AJ20" s="16"/>
-      <c r="AK20" s="16"/>
+      <c r="AJ20" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK20" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL20" s="16"/>
       <c r="AM20" s="16"/>
       <c r="AN20" s="16"/>
@@ -3043,7 +3141,7 @@
       </c>
       <c r="R21" s="4"/>
       <c r="S21" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T21" s="16" t="e">
@@ -3074,18 +3172,18 @@
       </c>
       <c r="AB21" s="16"/>
       <c r="AC21" s="16">
-        <f t="shared" ref="AC21:AC31" si="12">G21*R21</f>
+        <f t="shared" ref="AC21:AC31" si="14">G21*R21</f>
         <v>0</v>
       </c>
       <c r="AD21" s="6">
         <v>12</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AE31" si="13">MROUND(R21, AD21*AG21)/AD21</f>
+        <f t="shared" ref="AE21:AE31" si="15">MROUND(R21, AD21*AG21)/AD21</f>
         <v>0</v>
       </c>
       <c r="AF21" s="16">
-        <f t="shared" ref="AF21:AF31" si="14">AE21*AD21*G21</f>
+        <f t="shared" ref="AF21:AF31" si="16">AE21*AD21*G21</f>
         <v>0</v>
       </c>
       <c r="AG21" s="19">
@@ -3095,11 +3193,17 @@
         <v>70</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ21" s="16"/>
-      <c r="AK21" s="16"/>
+      <c r="AJ21" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK21" s="16">
+        <f t="shared" si="7"/>
+        <v>33.6</v>
+      </c>
       <c r="AL21" s="16"/>
       <c r="AM21" s="16"/>
       <c r="AN21" s="16"/>
@@ -3155,11 +3259,11 @@
         <v>79.8</v>
       </c>
       <c r="R22" s="4">
-        <f t="shared" ref="R22:R23" si="15">$R$1*Q22-P22-O22-F22</f>
+        <f t="shared" ref="R22:R23" si="17">$R$1*Q22-P22-O22-F22</f>
         <v>857.59999999999991</v>
       </c>
       <c r="S22" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>840</v>
       </c>
       <c r="T22" s="16">
@@ -3190,18 +3294,18 @@
       </c>
       <c r="AB22" s="16"/>
       <c r="AC22" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>171.51999999999998</v>
       </c>
       <c r="AD22" s="6">
         <v>12</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>70</v>
       </c>
       <c r="AF22" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>168</v>
       </c>
       <c r="AG22" s="19">
@@ -3211,11 +3315,17 @@
         <v>70</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AJ22" s="16"/>
-      <c r="AK22" s="16"/>
+      <c r="AJ22" s="16">
+        <f t="shared" si="6"/>
+        <v>15.96</v>
+      </c>
+      <c r="AK22" s="16">
+        <f t="shared" si="7"/>
+        <v>33.6</v>
+      </c>
       <c r="AL22" s="16"/>
       <c r="AM22" s="16"/>
       <c r="AN22" s="16"/>
@@ -3273,11 +3383,11 @@
         <v>41.2</v>
       </c>
       <c r="R23" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>181.40000000000009</v>
       </c>
       <c r="S23" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>168</v>
       </c>
       <c r="T23" s="16">
@@ -3308,18 +3418,18 @@
       </c>
       <c r="AB23" s="16"/>
       <c r="AC23" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>36.280000000000022</v>
       </c>
       <c r="AD23" s="6">
         <v>12</v>
       </c>
       <c r="AE23" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="AF23" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>33.6</v>
       </c>
       <c r="AG23" s="19">
@@ -3329,11 +3439,17 @@
         <v>70</v>
       </c>
       <c r="AI23" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="AJ23" s="16"/>
-      <c r="AK23" s="16"/>
+      <c r="AJ23" s="16">
+        <f t="shared" si="6"/>
+        <v>8.24</v>
+      </c>
+      <c r="AK23" s="16">
+        <f t="shared" si="7"/>
+        <v>33.6</v>
+      </c>
       <c r="AL23" s="16"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="16"/>
@@ -3388,7 +3504,7 @@
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T24" s="16" t="e">
@@ -3419,32 +3535,38 @@
       </c>
       <c r="AB24" s="16"/>
       <c r="AC24" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="19">
+        <v>12</v>
+      </c>
+      <c r="AH24" s="16">
+        <v>84</v>
+      </c>
+      <c r="AI24" s="8">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD24" s="6">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="8">
-        <f t="shared" si="13"/>
+      <c r="AJ24" s="16">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF24" s="16">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="19">
-        <v>12</v>
-      </c>
-      <c r="AH24" s="16">
-        <v>84</v>
-      </c>
-      <c r="AI24" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="16"/>
-      <c r="AK24" s="16"/>
+      <c r="AK24" s="16">
+        <f t="shared" si="7"/>
+        <v>60</v>
+      </c>
       <c r="AL24" s="16"/>
       <c r="AM24" s="16"/>
       <c r="AN24" s="16"/>
@@ -3501,7 +3623,7 @@
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T25" s="16">
@@ -3532,32 +3654,38 @@
       </c>
       <c r="AB25" s="16"/>
       <c r="AC25" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE25" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="19">
+        <v>14</v>
+      </c>
+      <c r="AH25" s="16">
+        <v>126</v>
+      </c>
+      <c r="AI25" s="8">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD25" s="6">
-        <v>3</v>
-      </c>
-      <c r="AE25" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AF25" s="16">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AG25" s="19">
-        <v>14</v>
-      </c>
-      <c r="AH25" s="16">
-        <v>126</v>
-      </c>
-      <c r="AI25" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="16"/>
+      <c r="AJ25" s="16">
+        <f t="shared" si="6"/>
+        <v>8.4</v>
+      </c>
+      <c r="AK25" s="16">
+        <f t="shared" si="7"/>
+        <v>210</v>
+      </c>
       <c r="AL25" s="16"/>
       <c r="AM25" s="16"/>
       <c r="AN25" s="16"/>
@@ -3616,7 +3744,7 @@
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T26" s="16">
@@ -3647,32 +3775,38 @@
       </c>
       <c r="AB26" s="16"/>
       <c r="AC26" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE26" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF26" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG26" s="19">
+        <v>14</v>
+      </c>
+      <c r="AH26" s="16">
+        <v>140</v>
+      </c>
+      <c r="AI26" s="8">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD26" s="6">
-        <v>6</v>
-      </c>
-      <c r="AE26" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AF26" s="16">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AG26" s="19">
-        <v>14</v>
-      </c>
-      <c r="AH26" s="16">
-        <v>140</v>
-      </c>
-      <c r="AI26" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="16"/>
-      <c r="AK26" s="16"/>
+      <c r="AJ26" s="16">
+        <f t="shared" si="6"/>
+        <v>12.85</v>
+      </c>
+      <c r="AK26" s="16">
+        <f t="shared" si="7"/>
+        <v>84</v>
+      </c>
       <c r="AL26" s="16"/>
       <c r="AM26" s="16"/>
       <c r="AN26" s="16"/>
@@ -3732,7 +3866,7 @@
         <v>619.79999999999995</v>
       </c>
       <c r="S27" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>588</v>
       </c>
       <c r="T27" s="16">
@@ -3763,18 +3897,18 @@
       </c>
       <c r="AB27" s="16"/>
       <c r="AC27" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>154.94999999999999</v>
       </c>
       <c r="AD27" s="6">
         <v>6</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>98</v>
       </c>
       <c r="AF27" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>147</v>
       </c>
       <c r="AG27" s="19">
@@ -3784,11 +3918,17 @@
         <v>140</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.7</v>
       </c>
-      <c r="AJ27" s="16"/>
-      <c r="AK27" s="16"/>
+      <c r="AJ27" s="16">
+        <f t="shared" si="6"/>
+        <v>10.35</v>
+      </c>
+      <c r="AK27" s="16">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
       <c r="AL27" s="16"/>
       <c r="AM27" s="16"/>
       <c r="AN27" s="16"/>
@@ -3839,7 +3979,7 @@
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T28" s="16" t="e">
@@ -3870,32 +4010,38 @@
       </c>
       <c r="AB28" s="16"/>
       <c r="AC28" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE28" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF28" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="19">
+        <v>12</v>
+      </c>
+      <c r="AH28" s="16">
+        <v>84</v>
+      </c>
+      <c r="AI28" s="8">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD28" s="6">
-        <v>6</v>
-      </c>
-      <c r="AE28" s="8">
-        <f t="shared" si="13"/>
+      <c r="AJ28" s="16">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF28" s="16">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="19">
-        <v>12</v>
-      </c>
-      <c r="AH28" s="16">
-        <v>84</v>
-      </c>
-      <c r="AI28" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="16"/>
-      <c r="AK28" s="16"/>
+      <c r="AK28" s="16">
+        <f t="shared" si="7"/>
+        <v>468</v>
+      </c>
       <c r="AL28" s="16"/>
       <c r="AM28" s="16"/>
       <c r="AN28" s="16"/>
@@ -3950,7 +4096,7 @@
       </c>
       <c r="R29" s="4"/>
       <c r="S29" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T29" s="16">
@@ -3981,32 +4127,38 @@
       </c>
       <c r="AB29" s="16"/>
       <c r="AC29" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD29" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE29" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF29" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="19">
+        <v>14</v>
+      </c>
+      <c r="AH29" s="16">
+        <v>70</v>
+      </c>
+      <c r="AI29" s="8">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD29" s="6">
-        <v>12</v>
-      </c>
-      <c r="AE29" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AF29" s="16">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AG29" s="19">
-        <v>14</v>
-      </c>
-      <c r="AH29" s="16">
-        <v>70</v>
-      </c>
-      <c r="AI29" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="16"/>
-      <c r="AK29" s="16"/>
+      <c r="AJ29" s="16">
+        <f t="shared" si="6"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="AK29" s="16">
+        <f t="shared" si="7"/>
+        <v>77.28</v>
+      </c>
       <c r="AL29" s="16"/>
       <c r="AM29" s="16"/>
       <c r="AN29" s="16"/>
@@ -4065,7 +4217,7 @@
       </c>
       <c r="R30" s="4"/>
       <c r="S30" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T30" s="16">
@@ -4096,32 +4248,38 @@
       </c>
       <c r="AB30" s="16"/>
       <c r="AC30" s="16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE30" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF30" s="16">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AG30" s="19">
+        <v>14</v>
+      </c>
+      <c r="AH30" s="16">
+        <v>70</v>
+      </c>
+      <c r="AI30" s="8">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD30" s="6">
-        <v>12</v>
-      </c>
-      <c r="AE30" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AF30" s="16">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AG30" s="19">
-        <v>14</v>
-      </c>
-      <c r="AH30" s="16">
-        <v>70</v>
-      </c>
-      <c r="AI30" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="16"/>
-      <c r="AK30" s="16"/>
+      <c r="AJ30" s="16">
+        <f t="shared" si="6"/>
+        <v>9.85</v>
+      </c>
+      <c r="AK30" s="16">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
       <c r="AL30" s="16"/>
       <c r="AM30" s="16"/>
       <c r="AN30" s="16"/>
@@ -4184,7 +4342,7 @@
         <v>759</v>
       </c>
       <c r="S31" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>840</v>
       </c>
       <c r="T31" s="16">
@@ -4215,18 +4373,18 @@
       </c>
       <c r="AB31" s="16"/>
       <c r="AC31" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>189.75</v>
       </c>
       <c r="AD31" s="6">
         <v>12</v>
       </c>
       <c r="AE31" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>70</v>
       </c>
       <c r="AF31" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>210</v>
       </c>
       <c r="AG31" s="19">
@@ -4236,11 +4394,17 @@
         <v>70</v>
       </c>
       <c r="AI31" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AJ31" s="16"/>
-      <c r="AK31" s="16"/>
+      <c r="AJ31" s="16">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="AK31" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL31" s="16"/>
       <c r="AM31" s="16"/>
       <c r="AN31" s="16"/>
@@ -4323,8 +4487,14 @@
       <c r="AG32" s="12"/>
       <c r="AH32" s="12"/>
       <c r="AI32" s="15"/>
-      <c r="AJ32" s="16"/>
-      <c r="AK32" s="16"/>
+      <c r="AJ32" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK32" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL32" s="16"/>
       <c r="AM32" s="16"/>
       <c r="AN32" s="16"/>
@@ -4383,7 +4553,7 @@
       </c>
       <c r="R33" s="4"/>
       <c r="S33" s="4">
-        <f t="shared" ref="S33:S68" si="16">AD33*AE33</f>
+        <f t="shared" ref="S33:S68" si="18">AD33*AE33</f>
         <v>0</v>
       </c>
       <c r="T33" s="16">
@@ -4414,18 +4584,18 @@
       </c>
       <c r="AB33" s="16"/>
       <c r="AC33" s="16">
-        <f t="shared" ref="AC33:AC70" si="17">G33*R33</f>
+        <f t="shared" ref="AC33:AC70" si="19">G33*R33</f>
         <v>0</v>
       </c>
       <c r="AD33" s="6">
         <v>12</v>
       </c>
       <c r="AE33" s="8">
-        <f t="shared" ref="AE33:AE68" si="18">MROUND(R33, AD33*AG33)/AD33</f>
+        <f t="shared" ref="AE33:AE68" si="20">MROUND(R33, AD33*AG33)/AD33</f>
         <v>0</v>
       </c>
       <c r="AF33" s="16">
-        <f t="shared" ref="AF33:AF68" si="19">AE33*AD33*G33</f>
+        <f t="shared" ref="AF33:AF68" si="21">AE33*AD33*G33</f>
         <v>0</v>
       </c>
       <c r="AG33" s="19">
@@ -4435,11 +4605,17 @@
         <v>70</v>
       </c>
       <c r="AI33" s="8">
-        <f t="shared" ref="AI33:AI68" si="20">AE33/AH33</f>
+        <f t="shared" ref="AI33:AI68" si="22">AE33/AH33</f>
         <v>0</v>
       </c>
-      <c r="AJ33" s="16"/>
-      <c r="AK33" s="16"/>
+      <c r="AJ33" s="16">
+        <f t="shared" si="6"/>
+        <v>9.65</v>
+      </c>
+      <c r="AK33" s="16">
+        <f t="shared" si="7"/>
+        <v>84</v>
+      </c>
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
       <c r="AN33" s="16"/>
@@ -4494,7 +4670,7 @@
       </c>
       <c r="R34" s="4"/>
       <c r="S34" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T34" s="16" t="e">
@@ -4525,18 +4701,18 @@
       </c>
       <c r="AB34" s="16"/>
       <c r="AC34" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD34" s="6">
         <v>12</v>
       </c>
       <c r="AE34" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF34" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG34" s="19">
@@ -4546,11 +4722,17 @@
         <v>70</v>
       </c>
       <c r="AI34" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ34" s="16"/>
-      <c r="AK34" s="16"/>
+      <c r="AJ34" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK34" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
       <c r="AN34" s="16"/>
@@ -4607,7 +4789,7 @@
       </c>
       <c r="R35" s="4"/>
       <c r="S35" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T35" s="16">
@@ -4638,18 +4820,18 @@
       </c>
       <c r="AB35" s="16"/>
       <c r="AC35" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD35" s="6">
         <v>8</v>
       </c>
       <c r="AE35" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF35" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG35" s="19">
@@ -4659,11 +4841,17 @@
         <v>84</v>
       </c>
       <c r="AI35" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ35" s="16"/>
-      <c r="AK35" s="16"/>
+      <c r="AJ35" s="16">
+        <f t="shared" si="6"/>
+        <v>9.1</v>
+      </c>
+      <c r="AK35" s="16">
+        <f t="shared" si="7"/>
+        <v>67.199999999999989</v>
+      </c>
       <c r="AL35" s="16"/>
       <c r="AM35" s="16"/>
       <c r="AN35" s="16"/>
@@ -4722,7 +4910,7 @@
       </c>
       <c r="R36" s="4"/>
       <c r="S36" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T36" s="16">
@@ -4753,18 +4941,18 @@
       </c>
       <c r="AB36" s="16"/>
       <c r="AC36" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD36" s="6">
         <v>8</v>
       </c>
       <c r="AE36" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF36" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG36" s="19">
@@ -4774,11 +4962,17 @@
         <v>84</v>
       </c>
       <c r="AI36" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ36" s="16"/>
-      <c r="AK36" s="16"/>
+      <c r="AJ36" s="16">
+        <f t="shared" si="6"/>
+        <v>15.399999999999999</v>
+      </c>
+      <c r="AK36" s="16">
+        <f t="shared" si="7"/>
+        <v>67.199999999999989</v>
+      </c>
       <c r="AL36" s="16"/>
       <c r="AM36" s="16"/>
       <c r="AN36" s="16"/>
@@ -4834,11 +5028,11 @@
         <v>21.2</v>
       </c>
       <c r="R37" s="4">
-        <f t="shared" ref="R37:R38" si="21">$R$1*Q37-P37-O37-F37</f>
+        <f t="shared" ref="R37:R38" si="23">$R$1*Q37-P37-O37-F37</f>
         <v>112.39999999999998</v>
       </c>
       <c r="S37" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>96</v>
       </c>
       <c r="T37" s="16">
@@ -4869,18 +5063,18 @@
       </c>
       <c r="AB37" s="16"/>
       <c r="AC37" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>78.679999999999978</v>
       </c>
       <c r="AD37" s="6">
         <v>8</v>
       </c>
       <c r="AE37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>12</v>
       </c>
       <c r="AF37" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AG37" s="19">
@@ -4890,11 +5084,17 @@
         <v>84</v>
       </c>
       <c r="AI37" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AJ37" s="16"/>
-      <c r="AK37" s="16"/>
+      <c r="AJ37" s="16">
+        <f t="shared" si="6"/>
+        <v>14.839999999999998</v>
+      </c>
+      <c r="AK37" s="16">
+        <f t="shared" si="7"/>
+        <v>67.199999999999989</v>
+      </c>
       <c r="AL37" s="16"/>
       <c r="AM37" s="16"/>
       <c r="AN37" s="16"/>
@@ -4934,7 +5134,7 @@
         <v>274</v>
       </c>
       <c r="L38" s="16">
-        <f t="shared" ref="L38:L69" si="22">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="24">E38-K38</f>
         <v>58</v>
       </c>
       <c r="M38" s="16"/>
@@ -4946,23 +5146,23 @@
         <v>360</v>
       </c>
       <c r="Q38" s="16">
-        <f t="shared" ref="Q38:Q69" si="23">E38/5</f>
+        <f t="shared" ref="Q38:Q69" si="25">E38/5</f>
         <v>66.400000000000006</v>
       </c>
       <c r="R38" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>358.80000000000018</v>
       </c>
       <c r="S38" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>360</v>
       </c>
       <c r="T38" s="16">
-        <f t="shared" ref="T38:T69" si="24">(F38+O38+P38+S38)/Q38</f>
+        <f t="shared" ref="T38:T69" si="26">(F38+O38+P38+S38)/Q38</f>
         <v>17.018072289156624</v>
       </c>
       <c r="U38" s="16">
-        <f t="shared" ref="U38:U69" si="25">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="U38:U69" si="27">(F38+O38+P38)/Q38</f>
         <v>11.596385542168674</v>
       </c>
       <c r="V38" s="16">
@@ -4985,18 +5185,18 @@
       </c>
       <c r="AB38" s="16"/>
       <c r="AC38" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>251.16000000000011</v>
       </c>
       <c r="AD38" s="6">
         <v>10</v>
       </c>
       <c r="AE38" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>36</v>
       </c>
       <c r="AF38" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AG38" s="19">
@@ -5006,11 +5206,17 @@
         <v>84</v>
       </c>
       <c r="AI38" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AJ38" s="16"/>
-      <c r="AK38" s="16"/>
+      <c r="AJ38" s="16">
+        <f t="shared" si="6"/>
+        <v>46.480000000000004</v>
+      </c>
+      <c r="AK38" s="16">
+        <f t="shared" si="7"/>
+        <v>251.99999999999997</v>
+      </c>
       <c r="AL38" s="16"/>
       <c r="AM38" s="16"/>
       <c r="AN38" s="16"/>
@@ -5052,7 +5258,7 @@
         <v>60</v>
       </c>
       <c r="L39" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>15</v>
       </c>
       <c r="M39" s="16"/>
@@ -5064,20 +5270,20 @@
         <v>0</v>
       </c>
       <c r="Q39" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>15</v>
       </c>
       <c r="R39" s="4"/>
       <c r="S39" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T39" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>23.933333333333334</v>
       </c>
       <c r="U39" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>23.933333333333334</v>
       </c>
       <c r="V39" s="16">
@@ -5100,18 +5306,18 @@
       </c>
       <c r="AB39" s="16"/>
       <c r="AC39" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD39" s="6">
         <v>10</v>
       </c>
       <c r="AE39" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF39" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG39" s="19">
@@ -5121,11 +5327,17 @@
         <v>84</v>
       </c>
       <c r="AI39" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ39" s="16"/>
-      <c r="AK39" s="16"/>
+      <c r="AJ39" s="16">
+        <f t="shared" si="6"/>
+        <v>10.5</v>
+      </c>
+      <c r="AK39" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL39" s="16"/>
       <c r="AM39" s="16"/>
       <c r="AN39" s="16"/>
@@ -5167,7 +5379,7 @@
         <v>156</v>
       </c>
       <c r="L40" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-90</v>
       </c>
       <c r="M40" s="16"/>
@@ -5179,20 +5391,20 @@
         <v>0</v>
       </c>
       <c r="Q40" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>13.2</v>
       </c>
       <c r="R40" s="4"/>
       <c r="S40" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T40" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>46.060606060606062</v>
       </c>
       <c r="U40" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>46.060606060606062</v>
       </c>
       <c r="V40" s="16">
@@ -5215,18 +5427,18 @@
       </c>
       <c r="AB40" s="16"/>
       <c r="AC40" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD40" s="6">
         <v>10</v>
       </c>
       <c r="AE40" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF40" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG40" s="19">
@@ -5236,11 +5448,17 @@
         <v>84</v>
       </c>
       <c r="AI40" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ40" s="16"/>
-      <c r="AK40" s="16"/>
+      <c r="AJ40" s="16">
+        <f t="shared" si="6"/>
+        <v>9.2399999999999984</v>
+      </c>
+      <c r="AK40" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL40" s="16"/>
       <c r="AM40" s="16"/>
       <c r="AN40" s="16"/>
@@ -5280,7 +5498,7 @@
         <v>259</v>
       </c>
       <c r="L41" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-94</v>
       </c>
       <c r="M41" s="16"/>
@@ -5292,23 +5510,23 @@
         <v>120</v>
       </c>
       <c r="Q41" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>33</v>
       </c>
       <c r="R41" s="4">
-        <f t="shared" ref="R41:R42" si="26">$R$1*Q41-P41-O41-F41</f>
+        <f t="shared" ref="R41:R42" si="28">$R$1*Q41-P41-O41-F41</f>
         <v>254</v>
       </c>
       <c r="S41" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>240</v>
       </c>
       <c r="T41" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.575757575757574</v>
       </c>
       <c r="U41" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>9.3030303030303028</v>
       </c>
       <c r="V41" s="16">
@@ -5331,18 +5549,18 @@
       </c>
       <c r="AB41" s="16"/>
       <c r="AC41" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>177.79999999999998</v>
       </c>
       <c r="AD41" s="6">
         <v>10</v>
       </c>
       <c r="AE41" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>24</v>
       </c>
       <c r="AF41" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>168</v>
       </c>
       <c r="AG41" s="19">
@@ -5352,11 +5570,17 @@
         <v>84</v>
       </c>
       <c r="AI41" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AJ41" s="16"/>
-      <c r="AK41" s="16"/>
+      <c r="AJ41" s="16">
+        <f t="shared" si="6"/>
+        <v>23.099999999999998</v>
+      </c>
+      <c r="AK41" s="16">
+        <f t="shared" si="7"/>
+        <v>84</v>
+      </c>
       <c r="AL41" s="16"/>
       <c r="AM41" s="16"/>
       <c r="AN41" s="16"/>
@@ -5398,7 +5622,7 @@
         <v>350</v>
       </c>
       <c r="L42" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M42" s="16"/>
@@ -5410,23 +5634,23 @@
         <v>660</v>
       </c>
       <c r="Q42" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>70</v>
       </c>
       <c r="R42" s="4">
+        <f t="shared" si="28"/>
+        <v>430</v>
+      </c>
+      <c r="S42" s="4">
+        <f t="shared" si="18"/>
+        <v>420</v>
+      </c>
+      <c r="T42" s="16">
         <f t="shared" si="26"/>
-        <v>430</v>
-      </c>
-      <c r="S42" s="4">
-        <f t="shared" si="16"/>
-        <v>420</v>
-      </c>
-      <c r="T42" s="16">
-        <f t="shared" si="24"/>
         <v>16.857142857142858</v>
       </c>
       <c r="U42" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>10.857142857142858</v>
       </c>
       <c r="V42" s="16">
@@ -5449,18 +5673,18 @@
       </c>
       <c r="AB42" s="16"/>
       <c r="AC42" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>430</v>
       </c>
       <c r="AD42" s="6">
         <v>5</v>
       </c>
       <c r="AE42" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>84</v>
       </c>
       <c r="AF42" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>420</v>
       </c>
       <c r="AG42" s="19">
@@ -5470,11 +5694,17 @@
         <v>144</v>
       </c>
       <c r="AI42" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="AJ42" s="16"/>
-      <c r="AK42" s="16"/>
+      <c r="AJ42" s="16">
+        <f t="shared" si="6"/>
+        <v>70</v>
+      </c>
+      <c r="AK42" s="16">
+        <f t="shared" si="7"/>
+        <v>660</v>
+      </c>
       <c r="AL42" s="16"/>
       <c r="AM42" s="16"/>
       <c r="AN42" s="16"/>
@@ -5514,7 +5744,7 @@
         <v>214</v>
       </c>
       <c r="L43" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-5</v>
       </c>
       <c r="M43" s="16"/>
@@ -5526,20 +5756,20 @@
         <v>0</v>
       </c>
       <c r="Q43" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>41.8</v>
       </c>
       <c r="R43" s="4"/>
       <c r="S43" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T43" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>21.387559808612441</v>
       </c>
       <c r="U43" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21.387559808612441</v>
       </c>
       <c r="V43" s="16">
@@ -5562,18 +5792,18 @@
       </c>
       <c r="AB43" s="16"/>
       <c r="AC43" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD43" s="6">
         <v>16</v>
       </c>
       <c r="AE43" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF43" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG43" s="19">
@@ -5583,11 +5813,17 @@
         <v>84</v>
       </c>
       <c r="AI43" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ43" s="16"/>
-      <c r="AK43" s="16"/>
+      <c r="AJ43" s="16">
+        <f t="shared" si="6"/>
+        <v>16.72</v>
+      </c>
+      <c r="AK43" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL43" s="16"/>
       <c r="AM43" s="16"/>
       <c r="AN43" s="16"/>
@@ -5629,7 +5865,7 @@
         <v>466</v>
       </c>
       <c r="L44" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-3</v>
       </c>
       <c r="M44" s="16"/>
@@ -5641,20 +5877,20 @@
         <v>720</v>
       </c>
       <c r="Q44" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>92.6</v>
       </c>
       <c r="R44" s="4"/>
       <c r="S44" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T44" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.349892008639308</v>
       </c>
       <c r="U44" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>16.349892008639308</v>
       </c>
       <c r="V44" s="16">
@@ -5677,18 +5913,18 @@
       </c>
       <c r="AB44" s="16"/>
       <c r="AC44" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD44" s="6">
         <v>10</v>
       </c>
       <c r="AE44" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF44" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG44" s="19">
@@ -5698,11 +5934,17 @@
         <v>84</v>
       </c>
       <c r="AI44" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ44" s="16"/>
-      <c r="AK44" s="16"/>
+      <c r="AJ44" s="16">
+        <f t="shared" si="6"/>
+        <v>64.819999999999993</v>
+      </c>
+      <c r="AK44" s="16">
+        <f t="shared" si="7"/>
+        <v>503.99999999999994</v>
+      </c>
       <c r="AL44" s="16"/>
       <c r="AM44" s="16"/>
       <c r="AN44" s="16"/>
@@ -5744,7 +5986,7 @@
         <v>244</v>
       </c>
       <c r="L45" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-28</v>
       </c>
       <c r="M45" s="16"/>
@@ -5756,20 +5998,20 @@
         <v>0</v>
       </c>
       <c r="Q45" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>43.2</v>
       </c>
       <c r="R45" s="4"/>
       <c r="S45" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T45" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>17.523148148148145</v>
       </c>
       <c r="U45" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>17.523148148148145</v>
       </c>
       <c r="V45" s="16">
@@ -5792,18 +6034,18 @@
       </c>
       <c r="AB45" s="16"/>
       <c r="AC45" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD45" s="6">
         <v>16</v>
       </c>
       <c r="AE45" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF45" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG45" s="19">
@@ -5813,11 +6055,17 @@
         <v>84</v>
       </c>
       <c r="AI45" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ45" s="16"/>
-      <c r="AK45" s="16"/>
+      <c r="AJ45" s="16">
+        <f t="shared" si="6"/>
+        <v>17.28</v>
+      </c>
+      <c r="AK45" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL45" s="16"/>
       <c r="AM45" s="16"/>
       <c r="AN45" s="16"/>
@@ -5861,7 +6109,7 @@
         <v>728</v>
       </c>
       <c r="L46" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>119</v>
       </c>
       <c r="M46" s="16"/>
@@ -5873,23 +6121,23 @@
         <v>960</v>
       </c>
       <c r="Q46" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>169.4</v>
       </c>
       <c r="R46" s="4">
-        <f t="shared" ref="R46:R47" si="27">$R$1*Q46-P46-O46-F46</f>
+        <f t="shared" ref="R46:R47" si="29">$R$1*Q46-P46-O46-F46</f>
         <v>1132.8000000000002</v>
       </c>
       <c r="S46" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1080</v>
       </c>
       <c r="T46" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.688311688311689</v>
       </c>
       <c r="U46" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>10.312868949232586</v>
       </c>
       <c r="V46" s="16">
@@ -5912,18 +6160,18 @@
       </c>
       <c r="AB46" s="16"/>
       <c r="AC46" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>792.96</v>
       </c>
       <c r="AD46" s="6">
         <v>10</v>
       </c>
       <c r="AE46" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>108</v>
       </c>
       <c r="AF46" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>756</v>
       </c>
       <c r="AG46" s="19">
@@ -5933,11 +6181,17 @@
         <v>84</v>
       </c>
       <c r="AI46" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.2857142857142858</v>
       </c>
-      <c r="AJ46" s="16"/>
-      <c r="AK46" s="16"/>
+      <c r="AJ46" s="16">
+        <f t="shared" si="6"/>
+        <v>118.58</v>
+      </c>
+      <c r="AK46" s="16">
+        <f t="shared" si="7"/>
+        <v>672</v>
+      </c>
       <c r="AL46" s="16"/>
       <c r="AM46" s="16"/>
       <c r="AN46" s="16"/>
@@ -5979,7 +6233,7 @@
         <v>291</v>
       </c>
       <c r="L47" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>34</v>
       </c>
       <c r="M47" s="16"/>
@@ -5991,23 +6245,23 @@
         <v>240</v>
       </c>
       <c r="Q47" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>65</v>
       </c>
       <c r="R47" s="4">
+        <f t="shared" si="29"/>
+        <v>420</v>
+      </c>
+      <c r="S47" s="4">
+        <f t="shared" si="18"/>
+        <v>480</v>
+      </c>
+      <c r="T47" s="16">
+        <f t="shared" si="26"/>
+        <v>17.923076923076923</v>
+      </c>
+      <c r="U47" s="16">
         <f t="shared" si="27"/>
-        <v>420</v>
-      </c>
-      <c r="S47" s="4">
-        <f t="shared" si="16"/>
-        <v>480</v>
-      </c>
-      <c r="T47" s="16">
-        <f t="shared" si="24"/>
-        <v>17.923076923076923</v>
-      </c>
-      <c r="U47" s="16">
-        <f t="shared" si="25"/>
         <v>10.538461538461538</v>
       </c>
       <c r="V47" s="16">
@@ -6030,18 +6284,18 @@
       </c>
       <c r="AB47" s="16"/>
       <c r="AC47" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>294</v>
       </c>
       <c r="AD47" s="6">
         <v>10</v>
       </c>
       <c r="AE47" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>48</v>
       </c>
       <c r="AF47" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>336</v>
       </c>
       <c r="AG47" s="19">
@@ -6051,11 +6305,17 @@
         <v>84</v>
       </c>
       <c r="AI47" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.5714285714285714</v>
       </c>
-      <c r="AJ47" s="16"/>
-      <c r="AK47" s="16"/>
+      <c r="AJ47" s="16">
+        <f t="shared" si="6"/>
+        <v>45.5</v>
+      </c>
+      <c r="AK47" s="16">
+        <f t="shared" si="7"/>
+        <v>168</v>
+      </c>
       <c r="AL47" s="16"/>
       <c r="AM47" s="16"/>
       <c r="AN47" s="16"/>
@@ -6095,7 +6355,7 @@
         <v>94</v>
       </c>
       <c r="L48" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-77</v>
       </c>
       <c r="M48" s="16"/>
@@ -6107,20 +6367,20 @@
         <v>180</v>
       </c>
       <c r="Q48" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>3.4</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T48" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>265.58823529411768</v>
       </c>
       <c r="U48" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>265.58823529411768</v>
       </c>
       <c r="V48" s="16">
@@ -6143,18 +6403,18 @@
       </c>
       <c r="AB48" s="16"/>
       <c r="AC48" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD48" s="6">
         <v>5</v>
       </c>
       <c r="AE48" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF48" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG48" s="19">
@@ -6164,11 +6424,17 @@
         <v>84</v>
       </c>
       <c r="AI48" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ48" s="16"/>
-      <c r="AK48" s="16"/>
+      <c r="AJ48" s="16">
+        <f t="shared" si="6"/>
+        <v>3.4</v>
+      </c>
+      <c r="AK48" s="16">
+        <f t="shared" si="7"/>
+        <v>180</v>
+      </c>
       <c r="AL48" s="16"/>
       <c r="AM48" s="16"/>
       <c r="AN48" s="16"/>
@@ -6210,7 +6476,7 @@
         <v>46</v>
       </c>
       <c r="L49" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-5</v>
       </c>
       <c r="M49" s="16"/>
@@ -6222,20 +6488,20 @@
         <v>288</v>
       </c>
       <c r="Q49" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T49" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>70.365853658536594</v>
       </c>
       <c r="U49" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>70.365853658536594</v>
       </c>
       <c r="V49" s="16">
@@ -6258,18 +6524,18 @@
       </c>
       <c r="AB49" s="16"/>
       <c r="AC49" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD49" s="6">
         <v>8</v>
       </c>
       <c r="AE49" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF49" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG49" s="19">
@@ -6279,11 +6545,17 @@
         <v>84</v>
       </c>
       <c r="AI49" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ49" s="16"/>
-      <c r="AK49" s="16"/>
+      <c r="AJ49" s="16">
+        <f t="shared" si="6"/>
+        <v>7.38</v>
+      </c>
+      <c r="AK49" s="16">
+        <f t="shared" si="7"/>
+        <v>259.2</v>
+      </c>
       <c r="AL49" s="16"/>
       <c r="AM49" s="16"/>
       <c r="AN49" s="16"/>
@@ -6323,7 +6595,7 @@
         <v>36</v>
       </c>
       <c r="L50" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-5</v>
       </c>
       <c r="M50" s="16"/>
@@ -6335,20 +6607,20 @@
         <v>192</v>
       </c>
       <c r="Q50" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>6.2</v>
       </c>
       <c r="R50" s="4"/>
       <c r="S50" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T50" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>77.258064516129025</v>
       </c>
       <c r="U50" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>77.258064516129025</v>
       </c>
       <c r="V50" s="16">
@@ -6371,18 +6643,18 @@
       </c>
       <c r="AB50" s="16"/>
       <c r="AC50" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD50" s="6">
         <v>8</v>
       </c>
       <c r="AE50" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF50" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG50" s="19">
@@ -6392,11 +6664,17 @@
         <v>84</v>
       </c>
       <c r="AI50" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ50" s="16"/>
-      <c r="AK50" s="16"/>
+      <c r="AJ50" s="16">
+        <f t="shared" si="6"/>
+        <v>5.58</v>
+      </c>
+      <c r="AK50" s="16">
+        <f t="shared" si="7"/>
+        <v>172.8</v>
+      </c>
       <c r="AL50" s="16"/>
       <c r="AM50" s="16"/>
       <c r="AN50" s="16"/>
@@ -6438,7 +6716,7 @@
         <v>565</v>
       </c>
       <c r="L51" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>35</v>
       </c>
       <c r="M51" s="16"/>
@@ -6450,23 +6728,23 @@
         <v>180</v>
       </c>
       <c r="Q51" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>120</v>
       </c>
       <c r="R51" s="4">
-        <f t="shared" ref="R51:R52" si="28">$R$1*Q51-P51-O51-F51</f>
+        <f t="shared" ref="R51:R52" si="30">$R$1*Q51-P51-O51-F51</f>
         <v>475</v>
       </c>
       <c r="S51" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>480</v>
       </c>
       <c r="T51" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>17.041666666666668</v>
       </c>
       <c r="U51" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>13.041666666666666</v>
       </c>
       <c r="V51" s="16">
@@ -6489,18 +6767,18 @@
       </c>
       <c r="AB51" s="16"/>
       <c r="AC51" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>475</v>
       </c>
       <c r="AD51" s="6">
         <v>5</v>
       </c>
       <c r="AE51" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>96</v>
       </c>
       <c r="AF51" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>480</v>
       </c>
       <c r="AG51" s="19">
@@ -6510,11 +6788,17 @@
         <v>144</v>
       </c>
       <c r="AI51" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="AJ51" s="16"/>
-      <c r="AK51" s="16"/>
+      <c r="AJ51" s="16">
+        <f t="shared" si="6"/>
+        <v>120</v>
+      </c>
+      <c r="AK51" s="16">
+        <f t="shared" si="7"/>
+        <v>180</v>
+      </c>
       <c r="AL51" s="16"/>
       <c r="AM51" s="16"/>
       <c r="AN51" s="16"/>
@@ -6554,7 +6838,7 @@
         <v>138</v>
       </c>
       <c r="L52" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="M52" s="16"/>
@@ -6566,23 +6850,23 @@
         <v>120</v>
       </c>
       <c r="Q52" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>27.8</v>
       </c>
       <c r="R52" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>164.60000000000002</v>
       </c>
       <c r="S52" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>180</v>
       </c>
       <c r="T52" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>17.553956834532375</v>
       </c>
       <c r="U52" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>11.079136690647482</v>
       </c>
       <c r="V52" s="16">
@@ -6605,18 +6889,18 @@
       </c>
       <c r="AB52" s="16"/>
       <c r="AC52" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>164.60000000000002</v>
       </c>
       <c r="AD52" s="6">
         <v>5</v>
       </c>
       <c r="AE52" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>36</v>
       </c>
       <c r="AF52" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>180</v>
       </c>
       <c r="AG52" s="19">
@@ -6626,11 +6910,17 @@
         <v>84</v>
       </c>
       <c r="AI52" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AJ52" s="16"/>
-      <c r="AK52" s="16"/>
+      <c r="AJ52" s="16">
+        <f t="shared" si="6"/>
+        <v>27.8</v>
+      </c>
+      <c r="AK52" s="16">
+        <f t="shared" si="7"/>
+        <v>120</v>
+      </c>
       <c r="AL52" s="16"/>
       <c r="AM52" s="16"/>
       <c r="AN52" s="16"/>
@@ -6672,7 +6962,7 @@
         <v>18.5</v>
       </c>
       <c r="L53" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7.3999999999999986</v>
       </c>
       <c r="M53" s="16"/>
@@ -6684,22 +6974,22 @@
         <v>51.8</v>
       </c>
       <c r="Q53" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5.18</v>
       </c>
       <c r="R53" s="4">
         <v>30</v>
       </c>
       <c r="S53" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>51.800000000000004</v>
       </c>
       <c r="T53" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>20.135135135135137</v>
       </c>
       <c r="U53" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>10.135135135135135</v>
       </c>
       <c r="V53" s="16">
@@ -6722,18 +7012,18 @@
       </c>
       <c r="AB53" s="16"/>
       <c r="AC53" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="AD53" s="6">
         <v>3.7</v>
       </c>
       <c r="AE53" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="AF53" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>51.800000000000004</v>
       </c>
       <c r="AG53" s="19">
@@ -6743,11 +7033,17 @@
         <v>126</v>
       </c>
       <c r="AI53" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AJ53" s="16"/>
-      <c r="AK53" s="16"/>
+      <c r="AJ53" s="16">
+        <f t="shared" si="6"/>
+        <v>5.18</v>
+      </c>
+      <c r="AK53" s="16">
+        <f t="shared" si="7"/>
+        <v>51.8</v>
+      </c>
       <c r="AL53" s="16"/>
       <c r="AM53" s="16"/>
       <c r="AN53" s="16"/>
@@ -6785,7 +7081,7 @@
         <v>111</v>
       </c>
       <c r="L54" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-16</v>
       </c>
       <c r="M54" s="16"/>
@@ -6797,20 +7093,20 @@
         <v>420</v>
       </c>
       <c r="Q54" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>19</v>
       </c>
       <c r="R54" s="4"/>
       <c r="S54" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T54" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>30.94736842105263</v>
       </c>
       <c r="U54" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>30.94736842105263</v>
       </c>
       <c r="V54" s="16">
@@ -6833,18 +7129,18 @@
       </c>
       <c r="AB54" s="16"/>
       <c r="AC54" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD54" s="6">
         <v>6</v>
       </c>
       <c r="AE54" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF54" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG54" s="19">
@@ -6854,11 +7150,17 @@
         <v>140</v>
       </c>
       <c r="AI54" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ54" s="16"/>
-      <c r="AK54" s="16"/>
+      <c r="AJ54" s="16">
+        <f t="shared" si="6"/>
+        <v>4.37</v>
+      </c>
+      <c r="AK54" s="16">
+        <f t="shared" si="7"/>
+        <v>96.600000000000009</v>
+      </c>
       <c r="AL54" s="16"/>
       <c r="AM54" s="16"/>
       <c r="AN54" s="16"/>
@@ -6900,7 +7202,7 @@
         <v>203</v>
       </c>
       <c r="L55" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-34</v>
       </c>
       <c r="M55" s="16"/>
@@ -6912,20 +7214,20 @@
         <v>672</v>
       </c>
       <c r="Q55" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>33.799999999999997</v>
       </c>
       <c r="R55" s="4"/>
       <c r="S55" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T55" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>29.911242603550299</v>
       </c>
       <c r="U55" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>29.911242603550299</v>
       </c>
       <c r="V55" s="16">
@@ -6948,18 +7250,18 @@
       </c>
       <c r="AB55" s="16"/>
       <c r="AC55" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD55" s="6">
         <v>12</v>
       </c>
       <c r="AE55" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF55" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG55" s="19">
@@ -6969,11 +7271,17 @@
         <v>70</v>
       </c>
       <c r="AI55" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ55" s="16"/>
-      <c r="AK55" s="16"/>
+      <c r="AJ55" s="16">
+        <f t="shared" si="6"/>
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="AK55" s="16">
+        <f t="shared" si="7"/>
+        <v>168</v>
+      </c>
       <c r="AL55" s="16"/>
       <c r="AM55" s="16"/>
       <c r="AN55" s="16"/>
@@ -7015,7 +7323,7 @@
         <v>272</v>
       </c>
       <c r="L56" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-10</v>
       </c>
       <c r="M56" s="16"/>
@@ -7027,23 +7335,23 @@
         <v>168</v>
       </c>
       <c r="Q56" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>52.4</v>
       </c>
       <c r="R56" s="4">
-        <f t="shared" ref="R56" si="29">$R$1*Q56-P56-O56-F56</f>
+        <f t="shared" ref="R56" si="31">$R$1*Q56-P56-O56-F56</f>
         <v>371.79999999999995</v>
       </c>
       <c r="S56" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>336</v>
       </c>
       <c r="T56" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.31679389312977</v>
       </c>
       <c r="U56" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>9.9045801526717554</v>
       </c>
       <c r="V56" s="16">
@@ -7066,18 +7374,18 @@
       </c>
       <c r="AB56" s="16"/>
       <c r="AC56" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>92.949999999999989</v>
       </c>
       <c r="AD56" s="6">
         <v>12</v>
       </c>
       <c r="AE56" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>28</v>
       </c>
       <c r="AF56" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>84</v>
       </c>
       <c r="AG56" s="19">
@@ -7087,11 +7395,17 @@
         <v>70</v>
       </c>
       <c r="AI56" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.4</v>
       </c>
-      <c r="AJ56" s="16"/>
-      <c r="AK56" s="16"/>
+      <c r="AJ56" s="16">
+        <f t="shared" si="6"/>
+        <v>13.1</v>
+      </c>
+      <c r="AK56" s="16">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
       <c r="AL56" s="16"/>
       <c r="AM56" s="16"/>
       <c r="AN56" s="16"/>
@@ -7131,7 +7445,7 @@
         <v>21</v>
       </c>
       <c r="L57" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M57" s="16"/>
@@ -7143,20 +7457,20 @@
         <v>0</v>
       </c>
       <c r="Q57" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>4.2</v>
       </c>
       <c r="R57" s="4"/>
       <c r="S57" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T57" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="U57" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>15</v>
       </c>
       <c r="V57" s="16">
@@ -7179,18 +7493,18 @@
       </c>
       <c r="AB57" s="16"/>
       <c r="AC57" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD57" s="6">
         <v>6</v>
       </c>
       <c r="AE57" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF57" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG57" s="19">
@@ -7200,11 +7514,17 @@
         <v>140</v>
       </c>
       <c r="AI57" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ57" s="16"/>
-      <c r="AK57" s="16"/>
+      <c r="AJ57" s="16">
+        <f t="shared" si="6"/>
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="AK57" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL57" s="16"/>
       <c r="AM57" s="16"/>
       <c r="AN57" s="16"/>
@@ -7244,7 +7564,7 @@
         <v>14</v>
       </c>
       <c r="L58" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M58" s="16"/>
@@ -7256,22 +7576,22 @@
         <v>0</v>
       </c>
       <c r="Q58" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>2.8</v>
       </c>
       <c r="R58" s="4">
         <v>50</v>
       </c>
       <c r="S58" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>84</v>
       </c>
       <c r="T58" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>40.357142857142861</v>
       </c>
       <c r="U58" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>10.357142857142858</v>
       </c>
       <c r="V58" s="16">
@@ -7294,18 +7614,18 @@
       </c>
       <c r="AB58" s="16"/>
       <c r="AC58" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
       <c r="AD58" s="6">
         <v>6</v>
       </c>
       <c r="AE58" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="AF58" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>15.12</v>
       </c>
       <c r="AG58" s="19">
@@ -7315,11 +7635,17 @@
         <v>140</v>
       </c>
       <c r="AI58" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.1</v>
       </c>
-      <c r="AJ58" s="16"/>
-      <c r="AK58" s="16"/>
+      <c r="AJ58" s="16">
+        <f t="shared" si="6"/>
+        <v>0.504</v>
+      </c>
+      <c r="AK58" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL58" s="16"/>
       <c r="AM58" s="16"/>
       <c r="AN58" s="16"/>
@@ -7359,7 +7685,7 @@
         <v>1</v>
       </c>
       <c r="L59" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M59" s="16"/>
@@ -7371,20 +7697,20 @@
         <v>0</v>
       </c>
       <c r="Q59" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.2</v>
       </c>
       <c r="R59" s="4"/>
       <c r="S59" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T59" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>375</v>
       </c>
       <c r="U59" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>375</v>
       </c>
       <c r="V59" s="16">
@@ -7409,18 +7735,18 @@
         <v>69</v>
       </c>
       <c r="AC59" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD59" s="6">
         <v>6</v>
       </c>
       <c r="AE59" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF59" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG59" s="19">
@@ -7430,11 +7756,17 @@
         <v>140</v>
       </c>
       <c r="AI59" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ59" s="16"/>
-      <c r="AK59" s="16"/>
+      <c r="AJ59" s="16">
+        <f t="shared" si="6"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="AK59" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL59" s="16"/>
       <c r="AM59" s="16"/>
       <c r="AN59" s="16"/>
@@ -7476,7 +7808,7 @@
         <v>307</v>
       </c>
       <c r="L60" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>41</v>
       </c>
       <c r="M60" s="16"/>
@@ -7488,23 +7820,23 @@
         <v>504</v>
       </c>
       <c r="Q60" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>69.599999999999994</v>
       </c>
       <c r="R60" s="4">
-        <f t="shared" ref="R60:R61" si="30">$R$1*Q60-P60-O60-F60</f>
+        <f t="shared" ref="R60:R61" si="32">$R$1*Q60-P60-O60-F60</f>
         <v>344.19999999999982</v>
       </c>
       <c r="S60" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>336</v>
       </c>
       <c r="T60" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.882183908045977</v>
       </c>
       <c r="U60" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>12.054597701149426</v>
       </c>
       <c r="V60" s="16">
@@ -7527,18 +7859,18 @@
       </c>
       <c r="AB60" s="16"/>
       <c r="AC60" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>103.25999999999995</v>
       </c>
       <c r="AD60" s="6">
         <v>12</v>
       </c>
       <c r="AE60" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>28</v>
       </c>
       <c r="AF60" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>100.8</v>
       </c>
       <c r="AG60" s="19">
@@ -7548,11 +7880,17 @@
         <v>70</v>
       </c>
       <c r="AI60" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.4</v>
       </c>
-      <c r="AJ60" s="16"/>
-      <c r="AK60" s="16"/>
+      <c r="AJ60" s="16">
+        <f t="shared" si="6"/>
+        <v>20.88</v>
+      </c>
+      <c r="AK60" s="16">
+        <f t="shared" si="7"/>
+        <v>151.19999999999999</v>
+      </c>
       <c r="AL60" s="16"/>
       <c r="AM60" s="16"/>
       <c r="AN60" s="16"/>
@@ -7594,7 +7932,7 @@
         <v>371</v>
       </c>
       <c r="L61" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>55</v>
       </c>
       <c r="M61" s="16"/>
@@ -7606,23 +7944,23 @@
         <v>672</v>
       </c>
       <c r="Q61" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>85.2</v>
       </c>
       <c r="R61" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>533.40000000000009</v>
       </c>
       <c r="S61" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>504</v>
       </c>
       <c r="T61" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.654929577464788</v>
       </c>
       <c r="U61" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>10.73943661971831</v>
       </c>
       <c r="V61" s="16">
@@ -7645,18 +7983,18 @@
       </c>
       <c r="AB61" s="16"/>
       <c r="AC61" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>160.02000000000001</v>
       </c>
       <c r="AD61" s="6">
         <v>12</v>
       </c>
       <c r="AE61" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>42</v>
       </c>
       <c r="AF61" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>151.19999999999999</v>
       </c>
       <c r="AG61" s="19">
@@ -7666,11 +8004,17 @@
         <v>70</v>
       </c>
       <c r="AI61" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
-      <c r="AJ61" s="16"/>
-      <c r="AK61" s="16"/>
+      <c r="AJ61" s="16">
+        <f t="shared" si="6"/>
+        <v>25.56</v>
+      </c>
+      <c r="AK61" s="16">
+        <f t="shared" si="7"/>
+        <v>201.6</v>
+      </c>
       <c r="AL61" s="16"/>
       <c r="AM61" s="16"/>
       <c r="AN61" s="16"/>
@@ -7708,7 +8052,7 @@
         <v>36</v>
       </c>
       <c r="L62" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-36</v>
       </c>
       <c r="M62" s="16"/>
@@ -7720,20 +8064,20 @@
         <v>392</v>
       </c>
       <c r="Q62" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R62" s="4"/>
       <c r="S62" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T62" s="16" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U62" s="16" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V62" s="16">
@@ -7756,18 +8100,18 @@
       </c>
       <c r="AB62" s="16"/>
       <c r="AC62" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD62" s="6">
         <v>14</v>
       </c>
       <c r="AE62" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF62" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG62" s="19">
@@ -7777,11 +8121,17 @@
         <v>70</v>
       </c>
       <c r="AI62" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ62" s="16"/>
-      <c r="AK62" s="16"/>
+      <c r="AJ62" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK62" s="16">
+        <f t="shared" si="7"/>
+        <v>117.6</v>
+      </c>
       <c r="AL62" s="16"/>
       <c r="AM62" s="16"/>
       <c r="AN62" s="16"/>
@@ -7823,7 +8173,7 @@
         <v>623</v>
       </c>
       <c r="L63" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>49</v>
       </c>
       <c r="M63" s="16"/>
@@ -7835,7 +8185,7 @@
         <v>504</v>
       </c>
       <c r="Q63" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>134.4</v>
       </c>
       <c r="R63" s="4">
@@ -7843,15 +8193,15 @@
         <v>1077.8000000000002</v>
       </c>
       <c r="S63" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1008</v>
       </c>
       <c r="T63" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.480654761904763</v>
       </c>
       <c r="U63" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8.980654761904761</v>
       </c>
       <c r="V63" s="16">
@@ -7874,18 +8224,18 @@
       </c>
       <c r="AB63" s="16"/>
       <c r="AC63" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>269.45000000000005</v>
       </c>
       <c r="AD63" s="6">
         <v>12</v>
       </c>
       <c r="AE63" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>84</v>
       </c>
       <c r="AF63" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>252</v>
       </c>
       <c r="AG63" s="19">
@@ -7895,11 +8245,17 @@
         <v>70</v>
       </c>
       <c r="AI63" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.2</v>
       </c>
-      <c r="AJ63" s="16"/>
-      <c r="AK63" s="16"/>
+      <c r="AJ63" s="16">
+        <f t="shared" si="6"/>
+        <v>33.6</v>
+      </c>
+      <c r="AK63" s="16">
+        <f t="shared" si="7"/>
+        <v>126</v>
+      </c>
       <c r="AL63" s="16"/>
       <c r="AM63" s="16"/>
       <c r="AN63" s="16"/>
@@ -7941,7 +8297,7 @@
         <v>295</v>
       </c>
       <c r="L64" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-56</v>
       </c>
       <c r="M64" s="16"/>
@@ -7953,20 +8309,20 @@
         <v>504</v>
       </c>
       <c r="Q64" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>47.8</v>
       </c>
       <c r="R64" s="4"/>
       <c r="S64" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T64" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>42.280334728033473</v>
       </c>
       <c r="U64" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>42.280334728033473</v>
       </c>
       <c r="V64" s="16">
@@ -7989,18 +8345,18 @@
       </c>
       <c r="AB64" s="16"/>
       <c r="AC64" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD64" s="6">
         <v>12</v>
       </c>
       <c r="AE64" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF64" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG64" s="19">
@@ -8010,11 +8366,17 @@
         <v>70</v>
       </c>
       <c r="AI64" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ64" s="16"/>
-      <c r="AK64" s="16"/>
+      <c r="AJ64" s="16">
+        <f t="shared" si="6"/>
+        <v>11.95</v>
+      </c>
+      <c r="AK64" s="16">
+        <f t="shared" si="7"/>
+        <v>126</v>
+      </c>
       <c r="AL64" s="16"/>
       <c r="AM64" s="16"/>
       <c r="AN64" s="16"/>
@@ -8056,7 +8418,7 @@
         <v>132</v>
       </c>
       <c r="L65" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>16</v>
       </c>
       <c r="M65" s="16"/>
@@ -8068,7 +8430,7 @@
         <v>252</v>
       </c>
       <c r="Q65" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>29.6</v>
       </c>
       <c r="R65" s="4">
@@ -8076,15 +8438,15 @@
         <v>249.20000000000005</v>
       </c>
       <c r="S65" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>252</v>
       </c>
       <c r="T65" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>17.094594594594593</v>
       </c>
       <c r="U65" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8.5810810810810807</v>
       </c>
       <c r="V65" s="16">
@@ -8107,18 +8469,18 @@
       </c>
       <c r="AB65" s="16"/>
       <c r="AC65" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>49.840000000000011</v>
       </c>
       <c r="AD65" s="6">
         <v>6</v>
       </c>
       <c r="AE65" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>42</v>
       </c>
       <c r="AF65" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>50.400000000000006</v>
       </c>
       <c r="AG65" s="19">
@@ -8128,11 +8490,17 @@
         <v>140</v>
       </c>
       <c r="AI65" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.3</v>
       </c>
-      <c r="AJ65" s="16"/>
-      <c r="AK65" s="16"/>
+      <c r="AJ65" s="16">
+        <f t="shared" si="6"/>
+        <v>5.9200000000000008</v>
+      </c>
+      <c r="AK65" s="16">
+        <f t="shared" si="7"/>
+        <v>50.400000000000006</v>
+      </c>
       <c r="AL65" s="16"/>
       <c r="AM65" s="16"/>
       <c r="AN65" s="16"/>
@@ -8172,7 +8540,7 @@
         <v>80</v>
       </c>
       <c r="L66" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-17</v>
       </c>
       <c r="M66" s="16"/>
@@ -8184,20 +8552,20 @@
         <v>168</v>
       </c>
       <c r="Q66" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>12.6</v>
       </c>
       <c r="R66" s="4"/>
       <c r="S66" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T66" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>66.666666666666671</v>
       </c>
       <c r="U66" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>66.666666666666671</v>
       </c>
       <c r="V66" s="16">
@@ -8220,18 +8588,18 @@
       </c>
       <c r="AB66" s="16"/>
       <c r="AC66" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD66" s="6">
         <v>6</v>
       </c>
       <c r="AE66" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF66" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG66" s="19">
@@ -8241,11 +8609,17 @@
         <v>140</v>
       </c>
       <c r="AI66" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ66" s="16"/>
-      <c r="AK66" s="16"/>
+      <c r="AJ66" s="16">
+        <f t="shared" si="6"/>
+        <v>2.8980000000000001</v>
+      </c>
+      <c r="AK66" s="16">
+        <f t="shared" si="7"/>
+        <v>38.64</v>
+      </c>
       <c r="AL66" s="16"/>
       <c r="AM66" s="16"/>
       <c r="AN66" s="16"/>
@@ -8287,7 +8661,7 @@
         <v>45.1</v>
       </c>
       <c r="L67" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>6.1999999999999957</v>
       </c>
       <c r="M67" s="16"/>
@@ -8299,20 +8673,20 @@
         <v>0</v>
       </c>
       <c r="Q67" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10.26</v>
       </c>
       <c r="R67" s="4"/>
       <c r="S67" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T67" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>15.263157894736842</v>
       </c>
       <c r="U67" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>15.263157894736842</v>
       </c>
       <c r="V67" s="16">
@@ -8335,18 +8709,18 @@
       </c>
       <c r="AB67" s="16"/>
       <c r="AC67" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AD67" s="6">
         <v>2.7</v>
       </c>
       <c r="AE67" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF67" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG67" s="19">
@@ -8356,11 +8730,17 @@
         <v>126</v>
       </c>
       <c r="AI67" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AJ67" s="16"/>
-      <c r="AK67" s="16"/>
+      <c r="AJ67" s="16">
+        <f t="shared" si="6"/>
+        <v>10.26</v>
+      </c>
+      <c r="AK67" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL67" s="16"/>
       <c r="AM67" s="16"/>
       <c r="AN67" s="16"/>
@@ -8402,7 +8782,7 @@
         <v>115</v>
       </c>
       <c r="L68" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>157.69999999999999</v>
       </c>
       <c r="M68" s="16"/>
@@ -8414,23 +8794,23 @@
         <v>420</v>
       </c>
       <c r="Q68" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>54.54</v>
       </c>
       <c r="R68" s="4">
-        <f t="shared" ref="R68" si="31">$R$1*Q68-P68-O68-F68</f>
+        <f t="shared" ref="R68" si="33">$R$1*Q68-P68-O68-F68</f>
         <v>207.57999999999993</v>
       </c>
       <c r="S68" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>180</v>
       </c>
       <c r="T68" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.494316098276496</v>
       </c>
       <c r="U68" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>13.193986065273194</v>
       </c>
       <c r="V68" s="16">
@@ -8453,18 +8833,18 @@
       </c>
       <c r="AB68" s="16"/>
       <c r="AC68" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>207.57999999999993</v>
       </c>
       <c r="AD68" s="6">
         <v>5</v>
       </c>
       <c r="AE68" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>36</v>
       </c>
       <c r="AF68" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>180</v>
       </c>
       <c r="AG68" s="19">
@@ -8474,11 +8854,17 @@
         <v>84</v>
       </c>
       <c r="AI68" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="AJ68" s="16"/>
-      <c r="AK68" s="16"/>
+      <c r="AJ68" s="16">
+        <f t="shared" si="6"/>
+        <v>54.54</v>
+      </c>
+      <c r="AK68" s="16">
+        <f t="shared" si="7"/>
+        <v>420</v>
+      </c>
       <c r="AL68" s="16"/>
       <c r="AM68" s="16"/>
       <c r="AN68" s="16"/>
@@ -8520,7 +8906,7 @@
         <v>130.4</v>
       </c>
       <c r="L69" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7.2999999999999829</v>
       </c>
       <c r="M69" s="12"/>
@@ -8530,17 +8916,17 @@
       </c>
       <c r="P69" s="12"/>
       <c r="Q69" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>27.54</v>
       </c>
       <c r="R69" s="14"/>
       <c r="S69" s="14"/>
       <c r="T69" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.3485838779956429</v>
       </c>
       <c r="U69" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5.3485838779956429</v>
       </c>
       <c r="V69" s="12">
@@ -8569,8 +8955,14 @@
       <c r="AG69" s="12"/>
       <c r="AH69" s="12"/>
       <c r="AI69" s="15"/>
-      <c r="AJ69" s="16"/>
-      <c r="AK69" s="16"/>
+      <c r="AJ69" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK69" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL69" s="16"/>
       <c r="AM69" s="16"/>
       <c r="AN69" s="16"/>
@@ -8609,7 +9001,7 @@
         <v>250</v>
       </c>
       <c r="S70" s="4">
-        <f t="shared" ref="S70" si="32">AD70*AE70</f>
+        <f t="shared" ref="S70" si="34">AD70*AE70</f>
         <v>288</v>
       </c>
       <c r="T70" s="16"/>
@@ -8636,18 +9028,18 @@
         <v>168</v>
       </c>
       <c r="AC70" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>200</v>
       </c>
       <c r="AD70" s="6">
         <v>8</v>
       </c>
       <c r="AE70" s="8">
-        <f t="shared" ref="AE70" si="33">MROUND(R70, AD70*AG70)/AD70</f>
+        <f t="shared" ref="AE70" si="35">MROUND(R70, AD70*AG70)/AD70</f>
         <v>36</v>
       </c>
       <c r="AF70" s="16">
-        <f t="shared" ref="AF70" si="34">AE70*AD70*G70</f>
+        <f t="shared" ref="AF70" si="36">AE70*AD70*G70</f>
         <v>230.4</v>
       </c>
       <c r="AG70" s="19">
@@ -8657,11 +9049,14 @@
         <v>84</v>
       </c>
       <c r="AI70" s="8">
-        <f t="shared" ref="AI70" si="35">AE70/AH70</f>
+        <f t="shared" ref="AI70" si="37">AE70/AH70</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="AJ70" s="16"/>
-      <c r="AK70" s="16"/>
+      <c r="AK70" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AL70" s="16"/>
       <c r="AM70" s="16"/>
       <c r="AN70" s="16"/>

--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ ЗПФ/дв 02,07,26 бррсч пок зпф.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ ЗПФ/дв 02,07,26 бррсч пок зпф.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DD72C6-A21B-4415-A447-5D06759946DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC043FBD-E87E-484A-8B23-D63DA958C079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$69</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -685,7 +677,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2200,7 +2192,7 @@
         <v>100.2</v>
       </c>
       <c r="R13" s="4">
-        <f t="shared" ref="R13:R16" si="13">$R$1*Q13-P13-O13-F13</f>
+        <f>$R$1*Q13-P13-O13-F13</f>
         <v>848.40000000000009</v>
       </c>
       <c r="S13" s="4">
@@ -2324,7 +2316,7 @@
         <v>82.8</v>
       </c>
       <c r="R14" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="R14:R16" si="13">$R$1*Q14-P14-O14-F14</f>
         <v>925.59999999999991</v>
       </c>
       <c r="S14" s="4">
